--- a/Dados/table_PROD__ANUAL_RS_1.xlsx
+++ b/Dados/table_PROD__ANUAL_RS_1.xlsx
@@ -356,7 +356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q15"/>
+  <dimension ref="A1:Q14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1159,61 +1159,6 @@
       </c>
       <c r="Q14">
         <v>83218.7752667977</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B15">
-        <v>30505.46309353427</v>
-      </c>
-      <c r="C15">
-        <v>48211.12356755985</v>
-      </c>
-      <c r="D15">
-        <v>33292.20532249309</v>
-      </c>
-      <c r="E15">
-        <v>104698.7605595203</v>
-      </c>
-      <c r="F15">
-        <v>13585.1436268811</v>
-      </c>
-      <c r="G15">
-        <v>29253.5344548008</v>
-      </c>
-      <c r="H15">
-        <v>17302.70599187461</v>
-      </c>
-      <c r="I15">
-        <v>13160.9130167087</v>
-      </c>
-      <c r="J15">
-        <v>36482.58041196429</v>
-      </c>
-      <c r="K15">
-        <v>87656.46293288308</v>
-      </c>
-      <c r="L15">
-        <v>253055.0050495057</v>
-      </c>
-      <c r="M15">
-        <v>14580.96303771252</v>
-      </c>
-      <c r="N15">
-        <v>30542.13602608892</v>
-      </c>
-      <c r="O15">
-        <v>22739.78636988625</v>
-      </c>
-      <c r="P15">
-        <v>24855.25654386944</v>
-      </c>
-      <c r="Q15">
-        <v>21216.95751005019</v>
       </c>
     </row>
   </sheetData>
@@ -1223,7 +1168,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q15"/>
+  <dimension ref="A1:Q14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -2026,61 +1971,6 @@
       </c>
       <c r="Q14">
         <v>40.94408148424671</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B15">
-        <v>14.51848417930958</v>
-      </c>
-      <c r="C15">
-        <v>22.53067531191212</v>
-      </c>
-      <c r="D15">
-        <v>15.58393762819894</v>
-      </c>
-      <c r="E15">
-        <v>48.70280619552878</v>
-      </c>
-      <c r="F15">
-        <v>6.481652605180841</v>
-      </c>
-      <c r="G15">
-        <v>13.76698449489846</v>
-      </c>
-      <c r="H15">
-        <v>7.999016342594508</v>
-      </c>
-      <c r="I15">
-        <v>5.96594686936209</v>
-      </c>
-      <c r="J15">
-        <v>17.89663898263388</v>
-      </c>
-      <c r="K15">
-        <v>43.1895211096825</v>
-      </c>
-      <c r="L15">
-        <v>127.1803252604508</v>
-      </c>
-      <c r="M15">
-        <v>7.869278965145488</v>
-      </c>
-      <c r="N15">
-        <v>16.43334474814222</v>
-      </c>
-      <c r="O15">
-        <v>11.518473272793</v>
-      </c>
-      <c r="P15">
-        <v>12.31438896432795</v>
-      </c>
-      <c r="Q15">
-        <v>10.44741075827901</v>
       </c>
     </row>
   </sheetData>
@@ -2090,7 +1980,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q15"/>
+  <dimension ref="A1:Q14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -2893,61 +2783,6 @@
       </c>
       <c r="Q14">
         <v>43.09380518416467</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B15">
-        <v>15.21497381886401</v>
-      </c>
-      <c r="C15">
-        <v>26.11322986310368</v>
-      </c>
-      <c r="D15">
-        <v>16.23395369931496</v>
-      </c>
-      <c r="E15">
-        <v>50.07301492276889</v>
-      </c>
-      <c r="F15">
-        <v>6.816261576690815</v>
-      </c>
-      <c r="G15">
-        <v>14.3813386511551</v>
-      </c>
-      <c r="H15">
-        <v>8.291797255035663</v>
-      </c>
-      <c r="I15">
-        <v>6.224120394242986</v>
-      </c>
-      <c r="J15">
-        <v>18.56940894027166</v>
-      </c>
-      <c r="K15">
-        <v>45.37094689647976</v>
-      </c>
-      <c r="L15">
-        <v>130.1427156284503</v>
-      </c>
-      <c r="M15">
-        <v>8.189708597740179</v>
-      </c>
-      <c r="N15">
-        <v>17.42269781202677</v>
-      </c>
-      <c r="O15">
-        <v>12.008860244239</v>
-      </c>
-      <c r="P15">
-        <v>12.85075647488458</v>
-      </c>
-      <c r="Q15">
-        <v>10.87760919165408</v>
       </c>
     </row>
   </sheetData>
@@ -2957,7 +2792,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q15"/>
+  <dimension ref="A1:Q14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -3712,61 +3547,6 @@
       </c>
       <c r="Q14">
         <v>0.2023064324777338</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B15">
-        <v>-73.2238121679086</v>
-      </c>
-      <c r="C15">
-        <v>-66.01334359339253</v>
-      </c>
-      <c r="D15">
-        <v>-73.6837226008159</v>
-      </c>
-      <c r="E15">
-        <v>-70.42317027228724</v>
-      </c>
-      <c r="F15">
-        <v>-73.80215945165861</v>
-      </c>
-      <c r="G15">
-        <v>-73.7320126503689</v>
-      </c>
-      <c r="H15">
-        <v>-73.51757762734233</v>
-      </c>
-      <c r="I15">
-        <v>-75.65326563808541</v>
-      </c>
-      <c r="J15">
-        <v>-76.36651110437488</v>
-      </c>
-      <c r="K15">
-        <v>-78.7011739053164</v>
-      </c>
-      <c r="L15">
-        <v>-67.25968640633376</v>
-      </c>
-      <c r="M15">
-        <v>-75.18806613006549</v>
-      </c>
-      <c r="N15">
-        <v>-76.44870540271293</v>
-      </c>
-      <c r="O15">
-        <v>-74.98945167455935</v>
-      </c>
-      <c r="P15">
-        <v>-74.53985137674555</v>
-      </c>
-      <c r="Q15">
-        <v>-74.50460254668606</v>
       </c>
     </row>
   </sheetData>
@@ -3776,7 +3556,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q15"/>
+  <dimension ref="A1:Q14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -4531,61 +4311,6 @@
       </c>
       <c r="Q14">
         <v>-0.2741199567411564</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B15">
-        <v>-72.09522029611252</v>
-      </c>
-      <c r="C15">
-        <v>-66.10383406051827</v>
-      </c>
-      <c r="D15">
-        <v>-73.74344435134489</v>
-      </c>
-      <c r="E15">
-        <v>-70.84303791550349</v>
-      </c>
-      <c r="F15">
-        <v>-73.12472217315106</v>
-      </c>
-      <c r="G15">
-        <v>-73.58761702353051</v>
-      </c>
-      <c r="H15">
-        <v>-73.6107919511383</v>
-      </c>
-      <c r="I15">
-        <v>-75.85946096917986</v>
-      </c>
-      <c r="J15">
-        <v>-75.89888764681291</v>
-      </c>
-      <c r="K15">
-        <v>-78.90694562497177</v>
-      </c>
-      <c r="L15">
-        <v>-67.35014439381565</v>
-      </c>
-      <c r="M15">
-        <v>-75.25976773811338</v>
-      </c>
-      <c r="N15">
-        <v>-76.28830829483604</v>
-      </c>
-      <c r="O15">
-        <v>-74.99002760729226</v>
-      </c>
-      <c r="P15">
-        <v>-74.38710553914621</v>
-      </c>
-      <c r="Q15">
-        <v>-74.48370953858455</v>
       </c>
     </row>
   </sheetData>
@@ -4595,7 +4320,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q15"/>
+  <dimension ref="A1:Q14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -5352,61 +5077,6 @@
         <v>0.3834399424364312</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B15">
-        <v>-72.31004688855884</v>
-      </c>
-      <c r="C15">
-        <v>-60.71407712366198</v>
-      </c>
-      <c r="D15">
-        <v>-74.20112332145585</v>
-      </c>
-      <c r="E15">
-        <v>-71.17662232979187</v>
-      </c>
-      <c r="F15">
-        <v>-73.52382450133841</v>
-      </c>
-      <c r="G15">
-        <v>-74.00529907010328</v>
-      </c>
-      <c r="H15">
-        <v>-73.58890709746763</v>
-      </c>
-      <c r="I15">
-        <v>-76.12112781922626</v>
-      </c>
-      <c r="J15">
-        <v>-76.0172244558662</v>
-      </c>
-      <c r="K15">
-        <v>-78.84758881173747</v>
-      </c>
-      <c r="L15">
-        <v>-67.72453576671786</v>
-      </c>
-      <c r="M15">
-        <v>-75.66125529408737</v>
-      </c>
-      <c r="N15">
-        <v>-76.79504180913895</v>
-      </c>
-      <c r="O15">
-        <v>-75.2460260990897</v>
-      </c>
-      <c r="P15">
-        <v>-74.67704513850489</v>
-      </c>
-      <c r="Q15">
-        <v>-74.75829960903248</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
